--- a/01_analyses_mask-PA/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-PA/results/SoIB_summaries.xlsx
@@ -512,10 +512,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>27.1</v>
       </c>
       <c r="E2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -523,16 +523,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="E3">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,16 +540,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D4">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="E4">
-        <v>84.59999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -557,13 +557,13 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -574,13 +574,13 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="E6">
         <v>1.2</v>
@@ -591,10 +591,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C7">
-        <v>294</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C8">
-        <v>284</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>747</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +753,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C3">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +764,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>463</v>
+        <v>414</v>
       </c>
       <c r="C4">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -813,7 +813,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D2">
         <v>22</v>
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -844,10 +844,10 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <v>15</v>
